--- a/data/trans_orig/Q5406-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2007</t>
+          <t>Población según si es capaz de tomar medicación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1733</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1921</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1856</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7936</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29260</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>63746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73467</t>
+          <t>73449</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1755</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53383</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63889</t>
+          <t>63942</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85058</t>
+          <t>84927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95599</t>
+          <t>95642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143172</t>
+          <t>143775</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157715</t>
+          <t>157616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,8%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1127</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6467</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1127</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5331</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6367</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>12165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72310</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81384</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121269</t>
+          <t>120511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132113</t>
+          <t>131446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -2101,97 +2101,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6966</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5998</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6075</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>824</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6380</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10321</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>54298</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65745</t>
+          <t>65616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73272</t>
+          <t>73268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>117608</t>
+          <t>118008</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>127232</t>
+          <t>126885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -2557,97 +2557,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6496</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6138</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6932</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>7086</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>9531</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13548</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19296</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27015</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31085</t>
+          <t>31166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40104</t>
+          <t>40103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>54721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65885</t>
+          <t>65674</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,03%</t>
         </is>
       </c>
     </row>
@@ -3013,97 +3013,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42873</t>
+          <t>42875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59344</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69168</t>
+          <t>69156</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106628</t>
+          <t>106525</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116359</t>
+          <t>116320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>12302</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>92663</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>103188</t>
+          <t>102449</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107065</t>
+          <t>107784</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116011</t>
+          <t>116154</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>204717</t>
+          <t>204031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>217009</t>
+          <t>216895</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16359</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>13409</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>13121</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19492</t>
+          <t>20169</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>98484</t>
+          <t>99113</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>108997</t>
+          <t>109101</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130644</t>
+          <t>130477</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>146020</t>
+          <t>145774</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>234050</t>
+          <t>232558</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>252866</t>
+          <t>252054</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>69796</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>458808</t>
+          <t>458908</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>479484</t>
+          <t>479717</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>618481</t>
+          <t>619463</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>645241</t>
+          <t>645182</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1087766</t>
+          <t>1086078</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1119455</t>
+          <t>1120894</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2012</t>
+          <t>Población según si es capaz de tomar medicación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8457</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8552</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17280</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43273</t>
+          <t>43295</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33811</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44653</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72560</t>
+          <t>73101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86103</t>
+          <t>86316</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1103</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16278</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>23190</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>15507</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,73%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57116</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72870</t>
+          <t>72735</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77347</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93008</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138495</t>
+          <t>140056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162419</t>
+          <t>162398</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10865</t>
+          <t>10987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>40626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57537</t>
+          <t>57973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72186</t>
+          <t>71719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>105314</t>
+          <t>104190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121940</t>
+          <t>121876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11691</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52192</t>
+          <t>52115</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61933</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>72125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83327</t>
+          <t>83315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>128605</t>
+          <t>129576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143119</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>967</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9779</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9561</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>23689</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30595</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38545</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>47860</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67030</t>
+          <t>65782</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77430</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>37922</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48517</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66989</t>
+          <t>68016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>98585</t>
+          <t>100339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114443</t>
+          <t>114434</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12886</t>
+          <t>12601</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17596</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>26668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96613</t>
+          <t>96504</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108339</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120272</t>
+          <t>120220</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>133966</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>222924</t>
+          <t>222295</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>240790</t>
+          <t>239935</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2062</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>17044</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>26323</t>
+          <t>27783</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106490</t>
+          <t>106047</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118690</t>
+          <t>118642</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>140950</t>
+          <t>143152</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>156754</t>
+          <t>157708</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>254821</t>
+          <t>252523</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>274071</t>
+          <t>273831</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46458</t>
+          <t>43950</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>36557</t>
+          <t>35307</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>65171</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>39603</t>
+          <t>39132</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>68343</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>71395</t>
+          <t>69131</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>110576</t>
+          <t>107561</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>485441</t>
+          <t>488591</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>518208</t>
+          <t>520073</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>638744</t>
+          <t>638025</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>674492</t>
+          <t>674913</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1139370</t>
+          <t>1138544</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1185609</t>
+          <t>1187332</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,15%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2016</t>
+          <t>Población según si es capaz de tomar medicación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>15594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26162</t>
+          <t>25469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34930</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>33099</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45654</t>
+          <t>45736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>62266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>78574</t>
+          <t>77697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,01%</t>
         </is>
       </c>
     </row>
@@ -9869,97 +9869,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6744</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1347</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6798</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7963</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1347</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6487</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>16070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2696</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87295</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97882</t>
+          <t>97693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111246</t>
+          <t>111179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185395</t>
+          <t>183805</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198630</t>
+          <t>198513</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1667</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12592</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>11728</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>7448</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,62 +10473,62 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2186</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6118</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6776</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>56098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>78652</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>128455</t>
+          <t>129983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141423</t>
+          <t>142146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,62 +10816,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2278</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3372</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>17881</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>56288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63853</t>
+          <t>63103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>75671</t>
+          <t>73693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89440</t>
+          <t>89409</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136692</t>
+          <t>136138</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151639</t>
+          <t>151617</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,62 +11272,62 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>799</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2056</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4373</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>799</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4124</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>9337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>37846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>41195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49385</t>
+          <t>49543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>81853</t>
+          <t>82384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90843</t>
+          <t>91011</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>6641</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>14705</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7582</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37149</t>
+          <t>37338</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45749</t>
+          <t>45295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>52424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64894</t>
+          <t>64900</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94143</t>
+          <t>94548</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108815</t>
+          <t>108967</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -12149,97 +12149,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>9003</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>2476</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8624</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>8420</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>8612</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101992</t>
+          <t>101711</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110345</t>
+          <t>110287</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>127380</t>
+          <t>126951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142448</t>
+          <t>141963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>233662</t>
+          <t>233486</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251143</t>
+          <t>251256</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -12605,97 +12605,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9502</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>11029</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>124666</t>
+          <t>127193</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>167124</t>
+          <t>168474</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>299848</t>
+          <t>299436</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>309191</t>
+          <t>309179</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>6351</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>24843</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32324</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>56482</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>43906</t>
+          <t>44508</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>78063</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>556532</t>
+          <t>556935</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>574821</t>
+          <t>574788</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>706155</t>
+          <t>702284</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>738860</t>
+          <t>736535</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1269472</t>
+          <t>1270660</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1306339</t>
+          <t>1306742</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2023</t>
+          <t>Población según si es capaz de tomar medicación en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,12 +13803,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7854</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>49019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55217</t>
+          <t>55235</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,12 +13994,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51611</t>
+          <t>51093</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>59452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103920</t>
+          <t>103878</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113933</t>
+          <t>113736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11208</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11103</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22319</t>
+          <t>22330</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,12 +14372,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14605</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28935</t>
+          <t>29746</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68976</t>
+          <t>69107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78165</t>
+          <t>78119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99256</t>
+          <t>98042</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112432</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171892</t>
+          <t>172090</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188454</t>
+          <t>188680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6464</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>455</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9182</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,12 +14793,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14813,12 +14813,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14848,12 +14848,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>14657</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62343</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70194</t>
+          <t>69766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75275</t>
+          <t>74593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82948</t>
+          <t>83030</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140282</t>
+          <t>140686</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151026</t>
+          <t>151212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5689</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -15171,12 +15171,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15191,12 +15191,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -15206,12 +15206,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>4872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11647</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8958</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17885</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63559</t>
+          <t>64456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71947</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88274</t>
+          <t>88208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95677</t>
+          <t>95919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156110</t>
+          <t>156082</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166185</t>
+          <t>166108</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,16%</t>
         </is>
       </c>
     </row>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>349</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29456</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>33852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,12 +15818,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15838,12 +15838,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47627</t>
+          <t>48397</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54349</t>
+          <t>54606</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15853,12 +15853,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79353</t>
+          <t>79375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>87146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2620</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3553</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,7 +16196,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52624</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58151</t>
+          <t>57942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51120</t>
+          <t>51387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57917</t>
+          <t>58370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106192</t>
+          <t>105646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114549</t>
+          <t>114202</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,31%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16544,7 +16544,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>718</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -16715,7 +16715,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118655</t>
+          <t>119509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>309428</t>
+          <t>310372</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>336761</t>
+          <t>336693</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>439381</t>
+          <t>439484</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>459299</t>
+          <t>459121</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -16945,97 +16945,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1196</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -17063,7 +17063,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>649</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>483</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17113,7 +17113,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -17171,7 +17171,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>145536</t>
+          <t>145811</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -17186,7 +17186,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>182394</t>
+          <t>182531</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>186158</t>
+          <t>186159</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,7 +17221,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>328319</t>
+          <t>328698</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>332579</t>
+          <t>332619</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3445</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13332</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>35457</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19071</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>41530</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,7 +17486,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15125</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>30398</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>69296</t>
+          <t>69590</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>46585</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>91806</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>611313</t>
+          <t>611514</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>628881</t>
+          <t>628300</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17667,7 +17667,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>989312</t>
+          <t>995333</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17682,7 +17682,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1553556</t>
+          <t>1553281</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1615413</t>
+          <t>1611627</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5406-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Provincia-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5621</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63746</t>
+          <t>65047</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73449</t>
+          <t>73462</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6149</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52952</t>
+          <t>53242</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63942</t>
+          <t>63860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84927</t>
+          <t>84694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95642</t>
+          <t>95740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143775</t>
+          <t>143304</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157616</t>
+          <t>157254</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12165</t>
+          <t>11745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45309</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71391</t>
+          <t>71570</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81313</t>
+          <t>81381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120511</t>
+          <t>121558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131446</t>
+          <t>132170</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>1674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>47763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54298</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>65616</t>
+          <t>65691</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73268</t>
+          <t>73250</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>118008</t>
+          <t>117886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>126885</t>
+          <t>127448</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>19970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27595</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31166</t>
+          <t>30696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40103</t>
+          <t>40098</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54721</t>
+          <t>54510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65674</t>
+          <t>65712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>278</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10357</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42875</t>
+          <t>42511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59952</t>
+          <t>60698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69156</t>
+          <t>70031</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>106525</t>
+          <t>106825</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116320</t>
+          <t>116135</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8104</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6542</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>3623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92663</t>
+          <t>93228</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>102449</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>107784</t>
+          <t>107164</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>116154</t>
+          <t>116197</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>204031</t>
+          <t>204781</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>216895</t>
+          <t>216912</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>13148</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1434</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20169</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>99113</t>
+          <t>98745</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>109101</t>
+          <t>109070</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>130477</t>
+          <t>130417</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>145774</t>
+          <t>145962</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>232558</t>
+          <t>232933</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>252054</t>
+          <t>252810</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>458908</t>
+          <t>457728</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>479717</t>
+          <t>479103</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>619463</t>
+          <t>617242</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>645162</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1086078</t>
+          <t>1087961</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1120894</t>
+          <t>1119725</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>8860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>35421</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>43290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33379</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44786</t>
+          <t>44550</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73101</t>
+          <t>72079</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86316</t>
+          <t>85930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,22%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,49 +5544,49 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7848</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17144</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
           <t>16,79%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>7848</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2684</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>16171</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>15,84%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>10</t>
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>24100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2302</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15507</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>56621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72735</t>
+          <t>73556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77717</t>
+          <t>76852</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93341</t>
+          <t>93090</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140056</t>
+          <t>139267</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162398</t>
+          <t>162517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20651</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40626</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52689</t>
+          <t>52711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57973</t>
+          <t>57545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71719</t>
+          <t>71572</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>121876</t>
+          <t>121717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52115</t>
+          <t>52026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61915</t>
+          <t>61939</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>72488</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83315</t>
+          <t>83206</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>129576</t>
+          <t>129900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>143017</t>
+          <t>143220</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5522</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7916</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9696</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6413</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9773</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23689</t>
+          <t>23449</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>38921</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47860</t>
+          <t>47864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65782</t>
+          <t>65829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>10785</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37922</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48529</t>
+          <t>48515</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68016</t>
+          <t>67994</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>100339</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114434</t>
+          <t>114416</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6835</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5018</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17578</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26668</t>
+          <t>25887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>96504</t>
+          <t>97448</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108422</t>
+          <t>108418</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120220</t>
+          <t>120785</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>133966</t>
+          <t>134511</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>222295</t>
+          <t>222256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>239935</t>
+          <t>240149</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>9070</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>26288</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>106047</t>
+          <t>106107</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>143152</t>
+          <t>142514</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>157708</t>
+          <t>157581</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>252523</t>
+          <t>255189</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>273831</t>
+          <t>273881</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>36879</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>65171</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>39132</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>67991</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>69131</t>
+          <t>70478</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>107561</t>
+          <t>106655</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>488591</t>
+          <t>487365</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>520073</t>
+          <t>519776</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>638025</t>
+          <t>640420</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>674913</t>
+          <t>676420</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1138544</t>
+          <t>1143677</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1187332</t>
+          <t>1188050</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,21%</t>
         </is>
       </c>
     </row>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9468,7 +9468,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8060</t>
+          <t>8265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21780</t>
+          <t>21538</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,4%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25469</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34911</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33099</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45736</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62266</t>
+          <t>62648</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77697</t>
+          <t>78404</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6744</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16070</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3952</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>96923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>111179</t>
+          <t>111263</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183805</t>
+          <t>183761</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198513</t>
+          <t>198424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7448</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56098</t>
+          <t>57377</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67305</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>78652</t>
+          <t>78663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129983</t>
+          <t>129939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142146</t>
+          <t>141450</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -10786,7 +10786,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17881</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>56288</t>
+          <t>56546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63103</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>73693</t>
+          <t>76070</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>89409</t>
+          <t>89398</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136138</t>
+          <t>134705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>151617</t>
+          <t>151414</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11312,7 +11312,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11327,7 +11327,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -11463,7 +11463,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37846</t>
+          <t>37551</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41195</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49543</t>
+          <t>49378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82384</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>91011</t>
+          <t>90888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12734</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14705</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11614</t>
+          <t>12495</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45295</t>
+          <t>46008</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52424</t>
+          <t>52107</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64900</t>
+          <t>64964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94548</t>
+          <t>94229</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>108967</t>
+          <t>108615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9003</t>
+          <t>8724</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>17612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>22810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>101711</t>
+          <t>101770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>110287</t>
+          <t>110377</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>126951</t>
+          <t>127337</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141963</t>
+          <t>142257</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>233486</t>
+          <t>233886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251256</t>
+          <t>250403</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12738,7 +12738,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12758,7 +12758,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7823</t>
+          <t>10161</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>11349</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>127060</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>168474</t>
+          <t>166136</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>299436</t>
+          <t>299116</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>309179</t>
+          <t>309177</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13081,7 +13081,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7280</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>26013</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>31752</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26479</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29265</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>56482</t>
+          <t>56478</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,7 +13224,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44508</t>
+          <t>43730</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>78063</t>
+          <t>76591</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>556935</t>
+          <t>555653</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>574788</t>
+          <t>574168</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>702284</t>
+          <t>704444</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>736535</t>
+          <t>737223</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1270660</t>
+          <t>1269943</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1306742</t>
+          <t>1307436</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -13748,7 +13748,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>885</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13783,32 +13783,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13818,32 +13818,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7982</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13871,12 +13871,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4971</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13896,32 +13896,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9089</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13931,32 +13931,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6168</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11545</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -13974,32 +13974,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49019</t>
+          <t>54375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55235</t>
+          <t>60214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -14009,32 +14009,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>57828</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51093</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59452</t>
+          <t>61125</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14044,32 +14044,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>109498</t>
+          <t>116273</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>103878</t>
+          <t>110937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113736</t>
+          <t>120467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55901</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -14122,17 +14122,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63409</t>
+          <t>65276</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -14157,17 +14157,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119310</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -14214,12 +14214,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>4583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14239,32 +14239,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6942</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14274,32 +14274,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13347</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -14317,32 +14317,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2752</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14352,32 +14352,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16127</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>12380</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>24177</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14387,32 +14387,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>23224</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15406</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -14430,32 +14430,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74549</t>
+          <t>81821</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69107</t>
+          <t>75397</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78119</t>
+          <t>85542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14465,32 +14465,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106466</t>
+          <t>110797</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98042</t>
+          <t>102988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>112347</t>
+          <t>117243</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14500,32 +14500,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>181015</t>
+          <t>192618</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172090</t>
+          <t>183448</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>188680</t>
+          <t>200507</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -14543,17 +14543,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80709</t>
+          <t>88373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14578,17 +14578,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128992</t>
+          <t>135328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14613,17 +14613,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>209700</t>
+          <t>223701</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14660,32 +14660,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6464</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14695,32 +14695,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4637</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14730,32 +14730,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>9100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -14773,32 +14773,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14808,32 +14808,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14843,32 +14843,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9512</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14657</t>
+          <t>14675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -14886,32 +14886,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>66898</t>
+          <t>65748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>61355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>68647</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14921,32 +14921,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>79633</t>
+          <t>78009</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74593</t>
+          <t>73639</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83030</t>
+          <t>81191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14956,32 +14956,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>146531</t>
+          <t>143757</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140686</t>
+          <t>137772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151212</t>
+          <t>148607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -14999,17 +14999,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73490</t>
+          <t>72285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -15034,17 +15034,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>87425</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -15069,17 +15069,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>160915</t>
+          <t>158135</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>569</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15126,12 +15126,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15151,32 +15151,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6063</t>
+          <t>6173</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15186,32 +15186,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>6907</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -15229,32 +15229,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4891</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15264,22 +15264,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8596</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15299,32 +15299,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18361</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -15342,32 +15342,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69225</t>
+          <t>77524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64456</t>
+          <t>72881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72052</t>
+          <t>80586</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15377,32 +15377,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92401</t>
+          <t>98599</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88208</t>
+          <t>94176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95919</t>
+          <t>102836</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15412,32 +15412,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>161625</t>
+          <t>176123</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>156082</t>
+          <t>169962</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>166108</t>
+          <t>181090</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -15455,17 +15455,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74668</t>
+          <t>83156</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15490,17 +15490,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>103636</t>
+          <t>110504</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178303</t>
+          <t>193660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15607,32 +15607,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>385</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15642,32 +15642,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -15685,32 +15685,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15720,32 +15720,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15755,32 +15755,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5455</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -15798,32 +15798,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>32259</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29564</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33852</t>
+          <t>35532</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15833,32 +15833,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>53754</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48397</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54606</t>
+          <t>56536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15868,22 +15868,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>84031</t>
+          <t>87645</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79375</t>
+          <t>82729</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87146</t>
+          <t>91177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -15911,17 +15911,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15946,17 +15946,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>61164</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15981,17 +15981,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93711</t>
+          <t>97667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -16028,32 +16028,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3397</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16063,32 +16063,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16098,32 +16098,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5842</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -16141,32 +16141,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16176,32 +16176,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16211,32 +16211,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12099</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -16254,32 +16254,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>55769</t>
+          <t>55609</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52440</t>
+          <t>52531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57942</t>
+          <t>57773</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16289,32 +16289,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>55025</t>
+          <t>56851</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51387</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58370</t>
+          <t>60209</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16324,32 +16324,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>110795</t>
+          <t>112459</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105646</t>
+          <t>107341</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>114202</t>
+          <t>116344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -16367,17 +16367,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>60261</t>
+          <t>60224</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -16402,17 +16402,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>66841</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>66841</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>64804</t>
+          <t>66841</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>125065</t>
+          <t>127064</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>125065</t>
+          <t>127064</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>125065</t>
+          <t>127064</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -16519,32 +16519,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>10356</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16554,32 +16554,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16607,12 +16607,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16632,32 +16632,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16667,32 +16667,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -16710,27 +16710,27 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>122417</t>
+          <t>150302</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119509</t>
+          <t>145098</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -16745,32 +16745,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>328984</t>
+          <t>153110</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>310372</t>
+          <t>146287</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>336693</t>
+          <t>157442</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16780,32 +16780,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>451402</t>
+          <t>303412</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>439484</t>
+          <t>295877</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>459121</t>
+          <t>308173</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -16823,17 +16823,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>123254</t>
+          <t>151341</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16858,17 +16858,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>338589</t>
+          <t>164124</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16893,17 +16893,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>461844</t>
+          <t>315465</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -17053,7 +17053,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -17063,12 +17063,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17088,32 +17088,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>531</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17123,32 +17123,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -17166,27 +17166,27 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>146302</t>
+          <t>162228</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>145811</t>
+          <t>159586</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>146460</t>
+          <t>162887</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -17201,32 +17201,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>185084</t>
+          <t>211023</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>182531</t>
+          <t>208165</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>186159</t>
+          <t>212235</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17236,32 +17236,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>331386</t>
+          <t>373252</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>328698</t>
+          <t>369556</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>332619</t>
+          <t>375035</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -17279,17 +17279,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>146460</t>
+          <t>162887</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>146460</t>
+          <t>162887</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>146460</t>
+          <t>162887</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17349,17 +17349,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>333102</t>
+          <t>375653</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>333102</t>
+          <t>375653</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>333102</t>
+          <t>375653</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17396,32 +17396,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17431,32 +17431,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>19989</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>35457</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17466,32 +17466,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20166</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41530</t>
+          <t>42853</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -17509,32 +17509,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17544,32 +17544,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>46355</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>69590</t>
+          <t>65989</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17579,32 +17579,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>46585</t>
+          <t>67337</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>90368</t>
+          <t>93038</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -17622,32 +17622,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>620883</t>
+          <t>685568</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>611514</t>
+          <t>675901</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>628300</t>
+          <t>693278</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17657,32 +17657,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>955400</t>
+          <t>819970</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>931358</t>
+          <t>805989</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>995333</t>
+          <t>831921</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17692,32 +17692,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1576283</t>
+          <t>1505538</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1553281</t>
+          <t>1489012</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1611627</t>
+          <t>1519932</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -17735,17 +17735,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>649558</t>
+          <t>715723</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17770,17 +17770,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1032393</t>
+          <t>901852</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17805,17 +17805,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1681951</t>
+          <t>1617575</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
